--- a/proceedings-content/corresponding_author_list_of_addresses.xlsx
+++ b/proceedings-content/corresponding_author_list_of_addresses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dr Ghassemi\Desktop\Coordination 2026\CoordinationStuff\ProceedingCoordination2026\proceedings-content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBA4C65-718E-40D8-9CD8-29D767139299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB21FE9-47E9-4B05-B309-DED06298EEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" tabRatio="208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8288" yWindow="2985" windowWidth="18195" windowHeight="12795" tabRatio="208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="authors" sheetId="1" r:id="rId1"/>
@@ -199,18 +199,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -241,32 +235,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -653,14 +646,14 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="51" style="4" customWidth="1"/>
-    <col min="4" max="4" width="45" style="4" customWidth="1"/>
-    <col min="5" max="5" width="64.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.796875" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="64.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -686,10 +679,10 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -701,10 +694,10 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -716,10 +709,10 @@
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -731,10 +724,10 @@
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -746,10 +739,10 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -758,13 +751,13 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -776,7 +769,7 @@
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -791,7 +784,7 @@
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -806,10 +799,10 @@
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -821,7 +814,7 @@
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -836,10 +829,10 @@
       <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -851,10 +844,10 @@
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -866,7 +859,7 @@
       <c r="C14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
